--- a/results/Int Task Remove ACC -0.6/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.6/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.005872884982739624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03037422017257225</v>
+        <v>0.03036820406912238</v>
       </c>
       <c r="F3" t="n">
         <v>0.002184021847673482</v>
@@ -1166,13 +1166,13 @@
         <v>0.02170738218569015</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.001521192539591351</v>
+        <v>-0.001521119343959427</v>
       </c>
       <c r="I3" t="n">
-        <v>9.112063465679943e-05</v>
+        <v>9.408284351126061e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0446288835618935</v>
+        <v>0.0446318325444945</v>
       </c>
       <c r="K3" t="n">
         <v>0.02369827246550908</v>
@@ -1184,10 +1184,10 @@
         <v>0.01620193060290426</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04007005449555578</v>
+        <v>0.04007008167121733</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02040754856512574</v>
+        <v>0.02041066868993073</v>
       </c>
       <c r="P3" t="n">
         <v>0.00727366524777433</v>
@@ -1196,7 +1196,7 @@
         <v>0.01600343528415791</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01558996069504552</v>
+        <v>0.01558715810370836</v>
       </c>
       <c r="S3" t="n">
         <v>0.2945550448381226</v>
@@ -1208,7 +1208,7 @@
         <v>0.1195994144672543</v>
       </c>
       <c r="V3" t="n">
-        <v>9.408284351126061e-05</v>
+        <v>9.694889310032263e-05</v>
       </c>
       <c r="W3" t="n">
         <v>0.009002547139726124</v>
@@ -1223,7 +1223,7 @@
         <v>0.002661589083606499</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03470825559115872</v>
+        <v>0.03470826606401791</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001387737771559038</v>
@@ -1238,7 +1238,7 @@
         <v>0.219134857984074</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08052404218324075</v>
+        <v>0.08052698942756728</v>
       </c>
       <c r="AG3" t="n">
         <v>0.08839249730421042</v>
@@ -1304,7 +1304,7 @@
         <v>0.00666491367052168</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.006484855965215755</v>
+        <v>0.006481908720889201</v>
       </c>
       <c r="BC3" t="n">
         <v>-9.507847258011238e-06</v>
@@ -1316,7 +1316,7 @@
         <v>-0.0009030771756960675</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.01421647633585122</v>
+        <v>0.01422238391173491</v>
       </c>
       <c r="BG3" t="n">
         <v>0.004759592890526729</v>
@@ -1355,7 +1355,7 @@
         <v>0.00275127113752375</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.002091660114180279</v>
+        <v>0.002091586918548356</v>
       </c>
       <c r="BT3" t="n">
         <v>0.001327178921898735</v>
@@ -1385,7 +1385,7 @@
         <v>0.0008728987040084535</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.002039517804002701</v>
+        <v>0.002033623315349592</v>
       </c>
       <c r="CD3" t="n">
         <v>-0.0005948769398728627</v>
@@ -1428,7 +1428,7 @@
         <v>0.01145012447400461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03270111276147303</v>
+        <v>0.03268634516299088</v>
       </c>
       <c r="F4" t="n">
         <v>0.002920908574377343</v>
@@ -1437,13 +1437,13 @@
         <v>0.05468928294964336</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002935620899505501</v>
+        <v>0.002945272753154862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001075446321685398</v>
+        <v>0.00107481857246709</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04427864464482235</v>
+        <v>0.04427809925961074</v>
       </c>
       <c r="K4" t="n">
         <v>0.01292209968582649</v>
@@ -1455,10 +1455,10 @@
         <v>0.03239192947161385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04062795411781884</v>
+        <v>0.04063808109722671</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02975231977534511</v>
+        <v>0.02976092186131991</v>
       </c>
       <c r="P4" t="n">
         <v>0.01821371798657882</v>
@@ -1467,7 +1467,7 @@
         <v>0.02031017484773797</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01792531510034494</v>
+        <v>0.01791850934239851</v>
       </c>
       <c r="S4" t="n">
         <v>0.1032683491624796</v>
@@ -1479,7 +1479,7 @@
         <v>0.05451432125979587</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00107481857246709</v>
+        <v>0.001071330355831541</v>
       </c>
       <c r="W4" t="n">
         <v>0.02960615851271703</v>
@@ -1494,7 +1494,7 @@
         <v>0.01305070478122668</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03088476664660157</v>
+        <v>0.03088835776433968</v>
       </c>
       <c r="AB4" t="n">
         <v>0.002761503144583464</v>
@@ -1509,7 +1509,7 @@
         <v>0.1512933346162925</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1102713846663821</v>
+        <v>0.1102644536620767</v>
       </c>
       <c r="AG4" t="n">
         <v>0.04074889328102505</v>
@@ -1575,7 +1575,7 @@
         <v>0.008704581431167679</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01477808628566346</v>
+        <v>0.0147795718627242</v>
       </c>
       <c r="BC4" t="n">
         <v>0.0006496816510989949</v>
@@ -1587,7 +1587,7 @@
         <v>0.003854980884221728</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.02480069184406648</v>
+        <v>0.02479469571506985</v>
       </c>
       <c r="BG4" t="n">
         <v>0.02423814092343936</v>
@@ -1626,7 +1626,7 @@
         <v>0.01177200767368808</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01309437990082745</v>
+        <v>0.01309525277224813</v>
       </c>
       <c r="BT4" t="n">
         <v>0.002375221859880209</v>
@@ -1656,7 +1656,7 @@
         <v>0.002169735804199412</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01250878885880777</v>
+        <v>0.01252265553119706</v>
       </c>
       <c r="CD4" t="n">
         <v>0.004499814999036689</v>
@@ -1708,10 +1708,10 @@
         <v>-0.0133967156439066</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.007404206280610726</v>
+        <v>-0.007433016421780414</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.001473622163277288</v>
+        <v>-0.001444149720011745</v>
       </c>
       <c r="J5" t="n">
         <v>-0.01060513447432767</v>
@@ -1780,7 +1780,7 @@
         <v>-0.1294724432655467</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1528735632183908</v>
+        <v>-0.1528440907751252</v>
       </c>
       <c r="AG5" t="n">
         <v>0.01709401709401711</v>
@@ -1858,7 +1858,7 @@
         <v>-0.01032143910350933</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.0318302387267904</v>
+        <v>-0.03180076628352486</v>
       </c>
       <c r="BG5" t="n">
         <v>-0.02189802534630115</v>
@@ -1927,7 +1927,7 @@
         <v>-0.001827291482463866</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.02443265546713819</v>
+        <v>-0.02449160035366928</v>
       </c>
       <c r="CD5" t="n">
         <v>-0.007644259369423001</v>
@@ -1982,7 +1982,7 @@
         <v>-0.003032696020484479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0003933375892087698</v>
+        <v>-0.0004155335051602344</v>
       </c>
       <c r="J6" t="n">
         <v>0.01509267494420046</v>
@@ -1997,7 +1997,7 @@
         <v>-0.003645962159384408</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01870371271668332</v>
+        <v>0.01868160838423417</v>
       </c>
       <c r="O6" t="n">
         <v>0.003122044731798476</v>
@@ -2009,7 +2009,7 @@
         <v>0.005242907033318573</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002743810460410062</v>
+        <v>0.002788123606643445</v>
       </c>
       <c r="S6" t="n">
         <v>0.2532194299970584</v>
@@ -2021,7 +2021,7 @@
         <v>0.09640929457403016</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0004155335051602344</v>
+        <v>-0.0003933375892087698</v>
       </c>
       <c r="W6" t="n">
         <v>-0.005609699076471145</v>
@@ -2036,7 +2036,7 @@
         <v>-0.005342995742301584</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01523069622563455</v>
+        <v>0.01523809486428504</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0004069974037743535</v>
@@ -2117,7 +2117,7 @@
         <v>0.0001794071762870275</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0009583889255230265</v>
+        <v>-0.0009657570363394124</v>
       </c>
       <c r="BC6" t="n">
         <v>-0.0004067618652026733</v>
@@ -2256,7 +2256,7 @@
         <v>-0.0001180899827373572</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02797725947193156</v>
+        <v>0.02799200438493657</v>
       </c>
       <c r="K7" t="n">
         <v>0.02533043389710127</v>
@@ -2280,7 +2280,7 @@
         <v>0.01150663112077603</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009613424515518006</v>
+        <v>0.00959867960251299</v>
       </c>
       <c r="S7" t="n">
         <v>0.2964936139591828</v>
@@ -2400,7 +2400,7 @@
         <v>-7.436049970255265e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0130533932022938</v>
+        <v>0.01306819486007947</v>
       </c>
       <c r="BG7" t="n">
         <v>-0.0008712066103989113</v>
@@ -2439,7 +2439,7 @@
         <v>-0.0006068110229114964</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.001988037797994147</v>
+        <v>0.001973266749249686</v>
       </c>
       <c r="BT7" t="n">
         <v>0.001046185876974698</v>
@@ -2512,7 +2512,7 @@
         <v>0.009667835795490395</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04049647216495166</v>
+        <v>0.04048926962965924</v>
       </c>
       <c r="F8" t="n">
         <v>0.00441173768307066</v>
@@ -2524,7 +2524,7 @@
         <v>0.0003655845657210138</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006966535504257077</v>
+        <v>0.0007189617003364734</v>
       </c>
       <c r="J8" t="n">
         <v>0.07773980348720409</v>
@@ -2551,7 +2551,7 @@
         <v>0.01554052629052733</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02240157984989051</v>
+        <v>0.02235836463813596</v>
       </c>
       <c r="S8" t="n">
         <v>0.3644490880758826</v>
@@ -2563,7 +2563,7 @@
         <v>0.1507046894235935</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0007189617003364734</v>
+        <v>0.0007038560857181297</v>
       </c>
       <c r="W8" t="n">
         <v>0.03109551075958515</v>
@@ -2783,7 +2783,7 @@
         <v>0.02507051081165781</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09289113622843544</v>
+        <v>0.09286139202855441</v>
       </c>
       <c r="F9" t="n">
         <v>0.007296898079763625</v>
@@ -2810,10 +2810,10 @@
         <v>0.0667256115531978</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1413741820345033</v>
+        <v>0.1414039262343843</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09422776911076444</v>
+        <v>0.09425897035881436</v>
       </c>
       <c r="P9" t="n">
         <v>0.04489859594383776</v>
